--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/87.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/87.xlsx
@@ -426,13 +426,13 @@
         <v>-9.723710334953633</v>
       </c>
       <c r="E2">
-        <v>-7.40488578999204</v>
+        <v>-5.449246175883565</v>
       </c>
       <c r="F2">
-        <v>-6.867187868191584</v>
+        <v>-6.704253384449039</v>
       </c>
       <c r="G2">
-        <v>-9.258564133801592</v>
+        <v>-8.297320752109888</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.587148393995491</v>
       </c>
       <c r="E3">
-        <v>-8.440520624702204</v>
+        <v>-6.184670354729231</v>
       </c>
       <c r="F3">
-        <v>-6.666692721303901</v>
+        <v>-6.541444398368019</v>
       </c>
       <c r="G3">
-        <v>-8.875911417099392</v>
+        <v>-8.27591476465296</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.586124889217174</v>
       </c>
       <c r="E4">
-        <v>-9.445198811095935</v>
+        <v>-5.556661579345507</v>
       </c>
       <c r="F4">
-        <v>-6.634539640564238</v>
+        <v>-6.54417883916466</v>
       </c>
       <c r="G4">
-        <v>-8.278308289077854</v>
+        <v>-8.525523277222929</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.718388387785195</v>
       </c>
       <c r="E5">
-        <v>-10.09798739624963</v>
+        <v>-6.87775330160318</v>
       </c>
       <c r="F5">
-        <v>-6.518474598655791</v>
+        <v>-6.622221817284609</v>
       </c>
       <c r="G5">
-        <v>-8.716803287936479</v>
+        <v>-7.754613090220545</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.9470538546386</v>
       </c>
       <c r="E6">
-        <v>-10.71107032130408</v>
+        <v>-8.511780691686905</v>
       </c>
       <c r="F6">
-        <v>-6.830414982446507</v>
+        <v>-6.582481719502706</v>
       </c>
       <c r="G6">
-        <v>-9.61414651962917</v>
+        <v>-8.123944171672717</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.23269604019976</v>
       </c>
       <c r="E7">
-        <v>-12.1170890451016</v>
+        <v>-9.39929367008018</v>
       </c>
       <c r="F7">
-        <v>-6.227591728427939</v>
+        <v>-6.20768108953425</v>
       </c>
       <c r="G7">
-        <v>-8.796981390352089</v>
+        <v>-8.400818337304123</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.53683435212603</v>
       </c>
       <c r="E8">
-        <v>-11.44894440458789</v>
+        <v>-9.666881199193423</v>
       </c>
       <c r="F8">
-        <v>-6.245081877770648</v>
+        <v>-6.284894043516595</v>
       </c>
       <c r="G8">
-        <v>-8.941903831879223</v>
+        <v>-8.518693621775412</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.82326779237903</v>
       </c>
       <c r="E9">
-        <v>-12.23382404807132</v>
+        <v>-10.76977292986551</v>
       </c>
       <c r="F9">
-        <v>-6.290062641926363</v>
+        <v>-5.807321183352416</v>
       </c>
       <c r="G9">
-        <v>-9.903786148860007</v>
+        <v>-8.337805413509635</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.06131593597677</v>
       </c>
       <c r="E10">
-        <v>-14.02414266158178</v>
+        <v>-10.96883106182067</v>
       </c>
       <c r="F10">
-        <v>-6.077330023397122</v>
+        <v>-5.829960464470926</v>
       </c>
       <c r="G10">
-        <v>-9.148025018245326</v>
+        <v>-8.671746763146999</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.23166037050254</v>
       </c>
       <c r="E11">
-        <v>-14.49255895598719</v>
+        <v>-12.16664413616754</v>
       </c>
       <c r="F11">
-        <v>-5.771664108498911</v>
+        <v>-5.458658858411895</v>
       </c>
       <c r="G11">
-        <v>-8.792108267318282</v>
+        <v>-8.676249105080407</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.31910886856802</v>
       </c>
       <c r="E12">
-        <v>-14.73727769136169</v>
+        <v>-13.16471075051007</v>
       </c>
       <c r="F12">
-        <v>-5.686576693985554</v>
+        <v>-5.458108822456436</v>
       </c>
       <c r="G12">
-        <v>-8.957499811914731</v>
+        <v>-8.478920727666608</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.3195378279552</v>
       </c>
       <c r="E13">
-        <v>-15.03908237007689</v>
+        <v>-13.20534474778089</v>
       </c>
       <c r="F13">
-        <v>-5.716860977864501</v>
+        <v>-5.130514365671316</v>
       </c>
       <c r="G13">
-        <v>-9.40465519790409</v>
+        <v>-8.652787268843593</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.24175516268545</v>
       </c>
       <c r="E14">
-        <v>-16.58319690873832</v>
+        <v>-14.6888728326937</v>
       </c>
       <c r="F14">
-        <v>-5.115941726321267</v>
+        <v>-4.778651229086378</v>
       </c>
       <c r="G14">
-        <v>-8.511572638320441</v>
+        <v>-8.392061944352751</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.09684269160238</v>
       </c>
       <c r="E15">
-        <v>-17.08741531864837</v>
+        <v>-15.6007807005663</v>
       </c>
       <c r="F15">
-        <v>-5.080210926768913</v>
+        <v>-4.716135169564502</v>
       </c>
       <c r="G15">
-        <v>-8.833321248736668</v>
+        <v>-8.321441386909019</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.9033025462315</v>
       </c>
       <c r="E16">
-        <v>-17.47137104433672</v>
+        <v>-17.05173547194194</v>
       </c>
       <c r="F16">
-        <v>-4.779762898140935</v>
+        <v>-4.360285929037294</v>
       </c>
       <c r="G16">
-        <v>-7.765296220675773</v>
+        <v>-8.221128546523563</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.68023934505949</v>
       </c>
       <c r="E17">
-        <v>-17.69678489501652</v>
+        <v>-17.48516930463809</v>
       </c>
       <c r="F17">
-        <v>-4.909999649576476</v>
+        <v>-4.309115189464159</v>
       </c>
       <c r="G17">
-        <v>-8.233960221033778</v>
+        <v>-7.735882023559348</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.44368925453235</v>
       </c>
       <c r="E18">
-        <v>-19.4771997358722</v>
+        <v>-18.46473710265929</v>
       </c>
       <c r="F18">
-        <v>-4.727317301134893</v>
+        <v>-3.824525229030866</v>
       </c>
       <c r="G18">
-        <v>-7.510036606870268</v>
+        <v>-8.258736343849682</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.21210989367694</v>
       </c>
       <c r="E19">
-        <v>-20.7640063814178</v>
+        <v>-19.87133094265578</v>
       </c>
       <c r="F19">
-        <v>-4.326113288569606</v>
+        <v>-3.658835181122909</v>
       </c>
       <c r="G19">
-        <v>-8.019062778443066</v>
+        <v>-7.445196261938102</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.00165748778851</v>
       </c>
       <c r="E20">
-        <v>-21.02949269859148</v>
+        <v>-20.00197288930307</v>
       </c>
       <c r="F20">
-        <v>-3.929317018954614</v>
+        <v>-3.284022125643411</v>
       </c>
       <c r="G20">
-        <v>-7.326586036357094</v>
+        <v>-7.708973909416152</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.82328819564726</v>
       </c>
       <c r="E21">
-        <v>-22.24918735934341</v>
+        <v>-21.5588396107701</v>
       </c>
       <c r="F21">
-        <v>-3.551950106772285</v>
+        <v>-2.721397470764195</v>
       </c>
       <c r="G21">
-        <v>-7.941791335010937</v>
+        <v>-7.312622155272448</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.685521369595675</v>
       </c>
       <c r="E22">
-        <v>-22.58004219881781</v>
+        <v>-22.16060587927937</v>
       </c>
       <c r="F22">
-        <v>-3.385245308795899</v>
+        <v>-2.704321505122886</v>
       </c>
       <c r="G22">
-        <v>-8.649096010567305</v>
+        <v>-6.753520671872634</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.585050942090849</v>
       </c>
       <c r="E23">
-        <v>-22.42775867488788</v>
+        <v>-22.35091047097771</v>
       </c>
       <c r="F23">
-        <v>-3.297925444131998</v>
+        <v>-2.4693236133575</v>
       </c>
       <c r="G23">
-        <v>-7.640362853114756</v>
+        <v>-7.183759170156318</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.511238426493776</v>
       </c>
       <c r="E24">
-        <v>-22.65104867125808</v>
+        <v>-22.43158523542436</v>
       </c>
       <c r="F24">
-        <v>-2.852503179605272</v>
+        <v>-2.281645381109632</v>
       </c>
       <c r="G24">
-        <v>-8.925450420549046</v>
+        <v>-7.262046951069003</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.452608228273816</v>
       </c>
       <c r="E25">
-        <v>-22.92232690668758</v>
+        <v>-21.9314922653353</v>
       </c>
       <c r="F25">
-        <v>-2.909845256329262</v>
+        <v>-2.14335689851888</v>
       </c>
       <c r="G25">
-        <v>-7.80882658397165</v>
+        <v>-7.378223925678646</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.38743307726017</v>
       </c>
       <c r="E26">
-        <v>-23.07234166513967</v>
+        <v>-22.35499062605862</v>
       </c>
       <c r="F26">
-        <v>-2.462074570215601</v>
+        <v>-2.189575657758079</v>
       </c>
       <c r="G26">
-        <v>-8.379617603670631</v>
+        <v>-7.270459047284291</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.290222262675961</v>
       </c>
       <c r="E27">
-        <v>-23.54018737182011</v>
+        <v>-22.97180501369538</v>
       </c>
       <c r="F27">
-        <v>-2.700732189166556</v>
+        <v>-2.015137221709156</v>
       </c>
       <c r="G27">
-        <v>-8.187033238014608</v>
+        <v>-6.857895551634776</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.138158862852309</v>
       </c>
       <c r="E28">
-        <v>-23.79688844941892</v>
+        <v>-23.14849701252667</v>
       </c>
       <c r="F28">
-        <v>-2.21734916003914</v>
+        <v>-2.491151922788669</v>
       </c>
       <c r="G28">
-        <v>-9.043322394474798</v>
+        <v>-7.66373861516755</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.90595005074899</v>
       </c>
       <c r="E29">
-        <v>-23.56600873061185</v>
+        <v>-21.97321309636796</v>
       </c>
       <c r="F29">
-        <v>-2.572769306251699</v>
+        <v>-2.182932151187627</v>
       </c>
       <c r="G29">
-        <v>-8.456852631101828</v>
+        <v>-7.222158187866324</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.576892130687195</v>
       </c>
       <c r="E30">
-        <v>-24.06903162338388</v>
+        <v>-22.07449241754951</v>
       </c>
       <c r="F30">
-        <v>-2.658649468369535</v>
+        <v>-2.414138605350399</v>
       </c>
       <c r="G30">
-        <v>-8.280536286225784</v>
+        <v>-7.445123429936238</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.145940632315824</v>
       </c>
       <c r="E31">
-        <v>-23.10247865966072</v>
+        <v>-22.15404864891626</v>
       </c>
       <c r="F31">
-        <v>-2.71949056900295</v>
+        <v>-2.427370946242719</v>
       </c>
       <c r="G31">
-        <v>-8.643977907163592</v>
+        <v>-7.733160755126067</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.615001345298981</v>
       </c>
       <c r="E32">
-        <v>-22.51850476552758</v>
+        <v>-21.32265704890005</v>
       </c>
       <c r="F32">
-        <v>-2.79956636072937</v>
+        <v>-2.332198158600278</v>
       </c>
       <c r="G32">
-        <v>-8.603221781029625</v>
+        <v>-7.426097724722047</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.004589192022945</v>
       </c>
       <c r="E33">
-        <v>-22.88973095078037</v>
+        <v>-20.82201613345606</v>
       </c>
       <c r="F33">
-        <v>-2.884995890980083</v>
+        <v>-2.245774587466205</v>
       </c>
       <c r="G33">
-        <v>-7.796438522563697</v>
+        <v>-7.215209352779394</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.340768635387007</v>
       </c>
       <c r="E34">
-        <v>-21.9252339142567</v>
+        <v>-20.86254597582471</v>
       </c>
       <c r="F34">
-        <v>-2.7827090840824</v>
+        <v>-2.409428508298082</v>
       </c>
       <c r="G34">
-        <v>-8.085627917601192</v>
+        <v>-6.967421640256024</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.64958060175108</v>
       </c>
       <c r="E35">
-        <v>-21.887629466097</v>
+        <v>-20.96657408072891</v>
       </c>
       <c r="F35">
-        <v>-2.816835335975532</v>
+        <v>-2.42812310384446</v>
       </c>
       <c r="G35">
-        <v>-8.434165462521202</v>
+        <v>-6.738146498388259</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.963873580559374</v>
       </c>
       <c r="E36">
-        <v>-21.34829274025747</v>
+        <v>-20.19550628296887</v>
       </c>
       <c r="F36">
-        <v>-2.978036460927718</v>
+        <v>-2.415968468943183</v>
       </c>
       <c r="G36">
-        <v>-7.26346717510535</v>
+        <v>-6.813547483590699</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.308314414061183</v>
       </c>
       <c r="E37">
-        <v>-21.42194384151822</v>
+        <v>-19.46237351197109</v>
       </c>
       <c r="F37">
-        <v>-3.22220023800508</v>
+        <v>-2.294731929339059</v>
       </c>
       <c r="G37">
-        <v>-7.657312846275826</v>
+        <v>-5.857455310758102</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.704185080798438</v>
       </c>
       <c r="E38">
-        <v>-20.39340059710407</v>
+        <v>-19.34692459561954</v>
       </c>
       <c r="F38">
-        <v>-2.661869332464217</v>
+        <v>-2.308221064126246</v>
       </c>
       <c r="G38">
-        <v>-7.213643464739318</v>
+        <v>-5.825419161574574</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.173002816125274</v>
       </c>
       <c r="E39">
-        <v>-20.19362696625569</v>
+        <v>-18.76541871982058</v>
       </c>
       <c r="F39">
-        <v>-2.901024800224254</v>
+        <v>-2.647676913752053</v>
       </c>
       <c r="G39">
-        <v>-7.577240681317473</v>
+        <v>-6.011167250692003</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.727728693093342</v>
       </c>
       <c r="E40">
-        <v>-20.34445232155516</v>
+        <v>-18.68652364565895</v>
       </c>
       <c r="F40">
-        <v>-3.393593595481312</v>
+        <v>-2.570706671418728</v>
       </c>
       <c r="G40">
-        <v>-6.77434069276911</v>
+        <v>-6.115863253371454</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.381613584129131</v>
       </c>
       <c r="E41">
-        <v>-19.13293608486109</v>
+        <v>-18.61593832130139</v>
       </c>
       <c r="F41">
-        <v>-2.87196650010145</v>
+        <v>-2.580805298426257</v>
       </c>
       <c r="G41">
-        <v>-6.759635249483668</v>
+        <v>-5.732240546826247</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.141637422706035</v>
       </c>
       <c r="E42">
-        <v>-18.64340351615791</v>
+        <v>-17.01114675941118</v>
       </c>
       <c r="F42">
-        <v>-2.81666634902536</v>
+        <v>-2.451320704592458</v>
       </c>
       <c r="G42">
-        <v>-6.673647139646638</v>
+        <v>-5.690881901404133</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.003756642494202</v>
       </c>
       <c r="E43">
-        <v>-17.76509239694822</v>
+        <v>-16.55326822402163</v>
       </c>
       <c r="F43">
-        <v>-3.274102425994887</v>
+        <v>-2.277686613291654</v>
       </c>
       <c r="G43">
-        <v>-6.6783646670401</v>
+        <v>-5.298194921172402</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.962401669904783</v>
       </c>
       <c r="E44">
-        <v>-17.34517153069096</v>
+        <v>-16.13946532614872</v>
       </c>
       <c r="F44">
-        <v>-3.127946109812345</v>
+        <v>-2.408932316223805</v>
       </c>
       <c r="G44">
-        <v>-6.72887366033276</v>
+        <v>-5.461431300622786</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.002041160540937</v>
       </c>
       <c r="E45">
-        <v>-16.75337243347256</v>
+        <v>-15.22077833268665</v>
       </c>
       <c r="F45">
-        <v>-3.380346343975743</v>
+        <v>-2.577095869196521</v>
       </c>
       <c r="G45">
-        <v>-6.540477134783916</v>
+        <v>-4.876941243482301</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.105184396391086</v>
       </c>
       <c r="E46">
-        <v>-16.66699179177625</v>
+        <v>-14.66326884065433</v>
       </c>
       <c r="F46">
-        <v>-3.417123371557832</v>
+        <v>-2.45287472184011</v>
       </c>
       <c r="G46">
-        <v>-7.187827830624082</v>
+        <v>-5.237714564715457</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.255358598605954</v>
       </c>
       <c r="E47">
-        <v>-15.07644680911418</v>
+        <v>-14.84993706772451</v>
       </c>
       <c r="F47">
-        <v>-3.141096442331787</v>
+        <v>-2.513438319393587</v>
       </c>
       <c r="G47">
-        <v>-6.636009547410664</v>
+        <v>-5.116982279443776</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.435269259360998</v>
       </c>
       <c r="E48">
-        <v>-14.02109047010061</v>
+        <v>-13.82786048419331</v>
       </c>
       <c r="F48">
-        <v>-3.274800739715447</v>
+        <v>-2.94152616764933</v>
       </c>
       <c r="G48">
-        <v>-6.627905331930529</v>
+        <v>-4.571947304040325</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.632861568009046</v>
       </c>
       <c r="E49">
-        <v>-13.79816728012502</v>
+        <v>-12.81514878490998</v>
       </c>
       <c r="F49">
-        <v>-3.301476655187799</v>
+        <v>-2.819349431043028</v>
       </c>
       <c r="G49">
-        <v>-6.001672606085372</v>
+        <v>-4.596630731581131</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.837990337903903</v>
       </c>
       <c r="E50">
-        <v>-13.88783106547689</v>
+        <v>-12.5781827970366</v>
       </c>
       <c r="F50">
-        <v>-3.552349379860435</v>
+        <v>-2.828126812043092</v>
       </c>
       <c r="G50">
-        <v>-5.879970330970685</v>
+        <v>-4.528459977836459</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.045858617606539</v>
       </c>
       <c r="E51">
-        <v>-12.72906702249817</v>
+        <v>-11.71486545526631</v>
       </c>
       <c r="F51">
-        <v>-3.813464039101284</v>
+        <v>-3.21345930517074</v>
       </c>
       <c r="G51">
-        <v>-6.423439418334061</v>
+        <v>-4.632954037238014</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.255868968843266</v>
       </c>
       <c r="E52">
-        <v>-12.42654684488976</v>
+        <v>-10.86963483868265</v>
       </c>
       <c r="F52">
-        <v>-3.894320981288544</v>
+        <v>-3.08756651239548</v>
       </c>
       <c r="G52">
-        <v>-6.354878020215755</v>
+        <v>-4.790632010727962</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.466988903104951</v>
       </c>
       <c r="E53">
-        <v>-12.00448401042687</v>
+        <v>-10.64194316557699</v>
       </c>
       <c r="F53">
-        <v>-3.719063289878252</v>
+        <v>-2.814681580728253</v>
       </c>
       <c r="G53">
-        <v>-6.392303737537215</v>
+        <v>-4.870399605496701</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.684667698564119</v>
       </c>
       <c r="E54">
-        <v>-11.52789382043762</v>
+        <v>-9.737489165921017</v>
       </c>
       <c r="F54">
-        <v>-3.781181733046784</v>
+        <v>-2.91040357595875</v>
       </c>
       <c r="G54">
-        <v>-5.820142151984976</v>
+        <v>-4.582474838855207</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.91316527501175</v>
       </c>
       <c r="E55">
-        <v>-11.25965871954128</v>
+        <v>-9.644582993179654</v>
       </c>
       <c r="F55">
-        <v>-3.757267594495366</v>
+        <v>-2.96174495921686</v>
       </c>
       <c r="G55">
-        <v>-6.593525316505197</v>
+        <v>-4.824018862491512</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.155729869570523</v>
       </c>
       <c r="E56">
-        <v>-11.51309023890654</v>
+        <v>-8.603749470308683</v>
       </c>
       <c r="F56">
-        <v>-3.89708358657688</v>
+        <v>-3.251166589346174</v>
       </c>
       <c r="G56">
-        <v>-6.761088578975408</v>
+        <v>-5.117240501995839</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.418467043914728</v>
       </c>
       <c r="E57">
-        <v>-9.621736841810955</v>
+        <v>-7.920176318850842</v>
       </c>
       <c r="F57">
-        <v>-4.428980781016651</v>
+        <v>-3.280732678686894</v>
       </c>
       <c r="G57">
-        <v>-6.248639303315003</v>
+        <v>-4.138027479116972</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.701359888602697</v>
       </c>
       <c r="E58">
-        <v>-10.31324840820424</v>
+        <v>-7.230104807191995</v>
       </c>
       <c r="F58">
-        <v>-3.854830222094883</v>
+        <v>-3.354546012848149</v>
       </c>
       <c r="G58">
-        <v>-6.390042634933893</v>
+        <v>-4.341162553406652</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.003484044964493</v>
       </c>
       <c r="E59">
-        <v>-9.154923627204266</v>
+        <v>-6.647829090811733</v>
       </c>
       <c r="F59">
-        <v>-4.092642906294982</v>
+        <v>-3.356783433203111</v>
       </c>
       <c r="G59">
-        <v>-6.265029814279934</v>
+        <v>-4.501435994599388</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.322468439447849</v>
       </c>
       <c r="E60">
-        <v>-8.619028541610563</v>
+        <v>-6.95432074012487</v>
       </c>
       <c r="F60">
-        <v>-4.322697929767863</v>
+        <v>-3.320094212565718</v>
       </c>
       <c r="G60">
-        <v>-5.574519536244289</v>
+        <v>-4.150137454699626</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.649639491852248</v>
       </c>
       <c r="E61">
-        <v>-8.69200490024417</v>
+        <v>-6.581953379422152</v>
       </c>
       <c r="F61">
-        <v>-4.2898937522496</v>
+        <v>-3.26569118338686</v>
       </c>
       <c r="G61">
-        <v>-6.280692005226227</v>
+        <v>-4.521828955121299</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.97741144297989</v>
       </c>
       <c r="E62">
-        <v>-8.112921758039315</v>
+        <v>-5.895536346287495</v>
       </c>
       <c r="F62">
-        <v>-4.371724026135149</v>
+        <v>-3.430706111861536</v>
       </c>
       <c r="G62">
-        <v>-6.249357691697025</v>
+        <v>-4.333051716835437</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.295105593058143</v>
       </c>
       <c r="E63">
-        <v>-7.327009622482133</v>
+        <v>-6.003141945657758</v>
       </c>
       <c r="F63">
-        <v>-4.399859524971235</v>
+        <v>-3.239788963068722</v>
       </c>
       <c r="G63">
-        <v>-7.233344521243521</v>
+        <v>-4.676464537260656</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.587685246720998</v>
       </c>
       <c r="E64">
-        <v>-9.026097598634058</v>
+        <v>-5.727593359239032</v>
       </c>
       <c r="F64">
-        <v>-4.713969817173584</v>
+        <v>-3.528098095776076</v>
       </c>
       <c r="G64">
-        <v>-7.462679252930994</v>
+        <v>-5.122239425760139</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.845323990412348</v>
       </c>
       <c r="E65">
-        <v>-6.705209384962924</v>
+        <v>-4.927348603447572</v>
       </c>
       <c r="F65">
-        <v>-4.437151797077865</v>
+        <v>-3.635248247695595</v>
       </c>
       <c r="G65">
-        <v>-7.297188391968366</v>
+        <v>-4.723828512291009</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.057987332241817</v>
       </c>
       <c r="E66">
-        <v>-7.881063888846594</v>
+        <v>-4.723087254857593</v>
       </c>
       <c r="F66">
-        <v>-4.632475032086169</v>
+        <v>-3.429941528748752</v>
       </c>
       <c r="G66">
-        <v>-6.580183817981934</v>
+        <v>-5.075252852921263</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.217296617743973</v>
       </c>
       <c r="E67">
-        <v>-7.365411082067178</v>
+        <v>-4.799690921171345</v>
       </c>
       <c r="F67">
-        <v>-4.437584204862127</v>
+        <v>-3.614542376095219</v>
       </c>
       <c r="G67">
-        <v>-7.016752079336704</v>
+        <v>-4.833013614721712</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.318664636221011</v>
       </c>
       <c r="E68">
-        <v>-7.331325258211443</v>
+        <v>-4.655223543378645</v>
       </c>
       <c r="F68">
-        <v>-4.350992475145286</v>
+        <v>-3.486215011523131</v>
       </c>
       <c r="G68">
-        <v>-6.743850568352423</v>
+        <v>-4.620234921276134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.359284476432673</v>
       </c>
       <c r="E69">
-        <v>-7.174726098552195</v>
+        <v>-4.339937597542612</v>
       </c>
       <c r="F69">
-        <v>-5.008857015426569</v>
+        <v>-3.862353454847108</v>
       </c>
       <c r="G69">
-        <v>-7.38697700808448</v>
+        <v>-4.522391747862975</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.338861013815195</v>
       </c>
       <c r="E70">
-        <v>-7.455373746703557</v>
+        <v>-4.188147677279509</v>
       </c>
       <c r="F70">
-        <v>-4.475342847816534</v>
+        <v>-3.715850052722793</v>
       </c>
       <c r="G70">
-        <v>-6.903365894616666</v>
+        <v>-4.460087280813891</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.259353702897537</v>
       </c>
       <c r="E71">
-        <v>-7.820101571755335</v>
+        <v>-4.377686956870551</v>
       </c>
       <c r="F71">
-        <v>-5.027479543008905</v>
+        <v>-3.984262628782306</v>
       </c>
       <c r="G71">
-        <v>-6.665817699446261</v>
+        <v>-4.416341732057961</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.122236084973749</v>
       </c>
       <c r="E72">
-        <v>-7.84748072560571</v>
+        <v>-5.014725509425571</v>
       </c>
       <c r="F72">
-        <v>-5.065036064317029</v>
+        <v>-4.026254229165018</v>
       </c>
       <c r="G72">
-        <v>-6.124556745957579</v>
+        <v>-4.640210753060097</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.928777259883734</v>
       </c>
       <c r="E73">
-        <v>-7.537117231016015</v>
+        <v>-4.573751767506647</v>
       </c>
       <c r="F73">
-        <v>-4.522769366729014</v>
+        <v>-4.022459478092793</v>
       </c>
       <c r="G73">
-        <v>-6.322398257929965</v>
+        <v>-4.366852386791397</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.684659238110504</v>
       </c>
       <c r="E74">
-        <v>-7.765732712819245</v>
+        <v>-5.42676683090949</v>
       </c>
       <c r="F74">
-        <v>-5.169368110332224</v>
+        <v>-3.752480459274587</v>
       </c>
       <c r="G74">
-        <v>-5.571199059068401</v>
+        <v>-3.775953113486882</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.39458422723406</v>
       </c>
       <c r="E75">
-        <v>-8.061442065520119</v>
+        <v>-4.444450249165636</v>
       </c>
       <c r="F75">
-        <v>-5.266306977277433</v>
+        <v>-4.259166291810155</v>
       </c>
       <c r="G75">
-        <v>-5.32423567238431</v>
+        <v>-2.854787196093596</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.064565888585498</v>
       </c>
       <c r="E76">
-        <v>-8.823561598641001</v>
+        <v>-5.747355619808505</v>
       </c>
       <c r="F76">
-        <v>-5.247677822755875</v>
+        <v>-4.308844313323444</v>
       </c>
       <c r="G76">
-        <v>-5.733564765041956</v>
+        <v>-2.639330271306748</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.705271229924473</v>
       </c>
       <c r="E77">
-        <v>-9.115145511520888</v>
+        <v>-6.499906487351181</v>
       </c>
       <c r="F77">
-        <v>-5.478107268294822</v>
+        <v>-4.295013062798901</v>
       </c>
       <c r="G77">
-        <v>-5.564425682895052</v>
+        <v>-3.200865005677927</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.325746794916302</v>
       </c>
       <c r="E78">
-        <v>-8.760407500130031</v>
+        <v>-6.29448132094123</v>
       </c>
       <c r="F78">
-        <v>-5.613224760467658</v>
+        <v>-4.544505727378473</v>
       </c>
       <c r="G78">
-        <v>-4.605913501273247</v>
+        <v>-2.888769946054214</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.937555208067363</v>
       </c>
       <c r="E79">
-        <v>-10.00831002547574</v>
+        <v>-7.446040561773748</v>
       </c>
       <c r="F79">
-        <v>-5.649710202723962</v>
+        <v>-4.679194125236658</v>
       </c>
       <c r="G79">
-        <v>-5.222065615951323</v>
+        <v>-2.360218176890795</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.555828564409718</v>
       </c>
       <c r="E80">
-        <v>-11.80597382382663</v>
+        <v>-7.738281103384747</v>
       </c>
       <c r="F80">
-        <v>-5.819888345220287</v>
+        <v>-4.961418071003047</v>
       </c>
       <c r="G80">
-        <v>-3.965024990325738</v>
+        <v>-1.842918952015357</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.19393971771792</v>
       </c>
       <c r="E81">
-        <v>-11.93835017601885</v>
+        <v>-7.698761110719808</v>
       </c>
       <c r="F81">
-        <v>-5.750765227293682</v>
+        <v>-4.648638965216996</v>
       </c>
       <c r="G81">
-        <v>-4.060663340409744</v>
+        <v>-2.030229618627321</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.869479011251523</v>
       </c>
       <c r="E82">
-        <v>-11.99818943155621</v>
+        <v>-8.626464295931157</v>
       </c>
       <c r="F82">
-        <v>-5.630216232633881</v>
+        <v>-5.017241750277706</v>
       </c>
       <c r="G82">
-        <v>-3.427690343846632</v>
+        <v>-1.863414539448986</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.596653111053762</v>
       </c>
       <c r="E83">
-        <v>-12.93896179275369</v>
+        <v>-9.585287154523218</v>
       </c>
       <c r="F83">
-        <v>-6.014864494286818</v>
+        <v>-5.506203833862975</v>
       </c>
       <c r="G83">
-        <v>-4.859941592138143</v>
+        <v>-1.531678013140777</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.386390015836083</v>
       </c>
       <c r="E84">
-        <v>-12.87854289254335</v>
+        <v>-10.45051098385074</v>
       </c>
       <c r="F84">
-        <v>-6.495330013421573</v>
+        <v>-5.314208150711718</v>
       </c>
       <c r="G84">
-        <v>-3.844835634522498</v>
+        <v>-1.20856545796237</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.249847333650516</v>
       </c>
       <c r="E85">
-        <v>-14.5045548836335</v>
+        <v>-11.52259550584864</v>
       </c>
       <c r="F85">
-        <v>-6.102196784461761</v>
+        <v>-5.843534092733199</v>
       </c>
       <c r="G85">
-        <v>-3.046944501375053</v>
+        <v>-1.525662751895921</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.190498052464794</v>
       </c>
       <c r="E86">
-        <v>-14.37946937459363</v>
+        <v>-12.71921759153149</v>
       </c>
       <c r="F86">
-        <v>-6.650596300116402</v>
+        <v>-5.608669568119663</v>
       </c>
       <c r="G86">
-        <v>-3.568249486353008</v>
+        <v>-0.7696897463667278</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.213146199627282</v>
       </c>
       <c r="E87">
-        <v>-17.69091599270258</v>
+        <v>-14.10932325766606</v>
       </c>
       <c r="F87">
-        <v>-6.803223822449614</v>
+        <v>-5.960877305544165</v>
       </c>
       <c r="G87">
-        <v>-2.642952008126711</v>
+        <v>-0.8637721400472756</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.320567045666867</v>
       </c>
       <c r="E88">
-        <v>-18.40318608394703</v>
+        <v>-15.42057007743106</v>
       </c>
       <c r="F88">
-        <v>-6.736690595207862</v>
+        <v>-6.085102594737591</v>
       </c>
       <c r="G88">
-        <v>-3.142066406354932</v>
+        <v>-0.2667483574951098</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.513393942771041</v>
       </c>
       <c r="E89">
-        <v>-19.30197949109341</v>
+        <v>-16.50431994847272</v>
       </c>
       <c r="F89">
-        <v>-7.084704722655692</v>
+        <v>-6.27712230054353</v>
       </c>
       <c r="G89">
-        <v>-3.017378019163822</v>
+        <v>-0.2550290262860898</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.793250445215941</v>
       </c>
       <c r="E90">
-        <v>-21.81948498922958</v>
+        <v>-18.70110080348964</v>
       </c>
       <c r="F90">
-        <v>-7.102526633143222</v>
+        <v>-6.576356770926407</v>
       </c>
       <c r="G90">
-        <v>-3.911771554781022</v>
+        <v>-0.213061240484749</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.156058262113995</v>
       </c>
       <c r="E91">
-        <v>-22.93803165454618</v>
+        <v>-19.95604057744326</v>
       </c>
       <c r="F91">
-        <v>-7.285348975675878</v>
+        <v>-6.3948511183805</v>
       </c>
       <c r="G91">
-        <v>-2.420668738437886</v>
+        <v>-0.8571444278776548</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.59770453849267</v>
       </c>
       <c r="E92">
-        <v>-25.52463260909138</v>
+        <v>-21.87330590281074</v>
       </c>
       <c r="F92">
-        <v>-7.102925077863969</v>
+        <v>-6.964296964638068</v>
       </c>
       <c r="G92">
-        <v>-3.244696628617878</v>
+        <v>-0.4550190823134622</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.110122460713108</v>
       </c>
       <c r="E93">
-        <v>-27.21876643467892</v>
+        <v>-23.69942210335183</v>
       </c>
       <c r="F93">
-        <v>-7.141290085757224</v>
+        <v>-7.021571115235028</v>
       </c>
       <c r="G93">
-        <v>-4.06490414924555</v>
+        <v>-1.025250619816306</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.674452838278464</v>
       </c>
       <c r="E94">
-        <v>-28.53324205641138</v>
+        <v>-26.01170621640839</v>
       </c>
       <c r="F94">
-        <v>-8.026333972072571</v>
+        <v>-6.927681468699524</v>
       </c>
       <c r="G94">
-        <v>-4.502439089897787</v>
+        <v>-1.323361935082138</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.274786115542382</v>
       </c>
       <c r="E95">
-        <v>-31.07795915485964</v>
+        <v>-28.4209042017031</v>
       </c>
       <c r="F95">
-        <v>-7.763695530994272</v>
+        <v>-7.276553370592953</v>
       </c>
       <c r="G95">
-        <v>-4.483820581784926</v>
+        <v>-1.59385005836829</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.88648905540995</v>
       </c>
       <c r="E96">
-        <v>-32.84339606793495</v>
+        <v>-30.44865070743571</v>
       </c>
       <c r="F96">
-        <v>-7.533011776662666</v>
+        <v>-7.276113507502067</v>
       </c>
       <c r="G96">
-        <v>-5.220142188993005</v>
+        <v>-2.624141488372572</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.481262210857121</v>
       </c>
       <c r="E97">
-        <v>-35.52101029308631</v>
+        <v>-34.00400319983479</v>
       </c>
       <c r="F97">
-        <v>-7.932351962571654</v>
+        <v>-7.519024793066396</v>
       </c>
       <c r="G97">
-        <v>-4.884337002217033</v>
+        <v>-2.218844640181758</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.033819660447794</v>
       </c>
       <c r="E98">
-        <v>-37.6495221382006</v>
+        <v>-35.71659055700358</v>
       </c>
       <c r="F98">
-        <v>-8.061292733205516</v>
+        <v>-7.279435260787293</v>
       </c>
       <c r="G98">
-        <v>-5.747982190865482</v>
+        <v>-3.548601398577433</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.513847075295487</v>
       </c>
       <c r="E99">
-        <v>-40.77972111262655</v>
+        <v>-38.35110503078694</v>
       </c>
       <c r="F99">
-        <v>-8.537570440935419</v>
+        <v>-7.346522251637816</v>
       </c>
       <c r="G99">
-        <v>-5.787625973698255</v>
+        <v>-4.332919295013867</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.898883716883168</v>
       </c>
       <c r="E100">
-        <v>-42.00623791947103</v>
+        <v>-40.83630665958939</v>
       </c>
       <c r="F100">
-        <v>-8.214194030965352</v>
+        <v>-7.582271886821243</v>
       </c>
       <c r="G100">
-        <v>-7.582981167282569</v>
+        <v>-4.762254014365329</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.170957727176487</v>
       </c>
       <c r="E101">
-        <v>-45.59634871411598</v>
+        <v>-43.71620102595237</v>
       </c>
       <c r="F101">
-        <v>-8.424093218793317</v>
+        <v>-7.573424094591942</v>
       </c>
       <c r="G101">
-        <v>-7.31184417707072</v>
+        <v>-5.319448623534523</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.318325744764387</v>
       </c>
       <c r="E102">
-        <v>-47.44048144849658</v>
+        <v>-45.92314604087951</v>
       </c>
       <c r="F102">
-        <v>-8.650237933941282</v>
+        <v>-7.517623609604561</v>
       </c>
       <c r="G102">
-        <v>-8.28795521877929</v>
+        <v>-6.226789702755814</v>
       </c>
     </row>
   </sheetData>
